--- a/spreadsheets/CryptoBestBidAskNew.xlsx
+++ b/spreadsheets/CryptoBestBidAskNew.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cc475311eb7e8809/Research 2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micha\git-projects\trading\spreadsheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="99" documentId="13_ncr:1_{437486C6-8647-1D4A-85BE-CA2631131FFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E4DC3684-2378-6448-A967-634721B92B20}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51F1CB8A-C0CB-40C6-9282-87FAB863343B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="1464" yWindow="1188" windowWidth="21132" windowHeight="11448" firstSheet="1" activeTab="3" xr2:uid="{48EF623B-BF7B-294B-8A9D-11BB0CCA5B79}"/>
+    <workbookView xWindow="29730" yWindow="3885" windowWidth="24930" windowHeight="9690" firstSheet="1" activeTab="3" xr2:uid="{48EF623B-BF7B-294B-8A9D-11BB0CCA5B79}"/>
   </bookViews>
   <sheets>
     <sheet name="BINANCE" sheetId="25" r:id="rId1"/>
@@ -1527,27 +1527,27 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0031EC5F-B12E-8847-9D65-17ED9F73C586}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:X14"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.3984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.09765625" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.3984375" customWidth="1"/>
-    <col min="4" max="5" width="10.8984375" style="21"/>
-    <col min="6" max="6" width="6.8984375" style="27" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="10.8984375" style="21"/>
-    <col min="9" max="9" width="5.3984375" customWidth="1"/>
+    <col min="1" max="1" width="8.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.375" customWidth="1"/>
+    <col min="4" max="5" width="10.875" style="21"/>
+    <col min="6" max="6" width="6.875" style="27" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="10.875" style="21"/>
+    <col min="9" max="9" width="5.375" customWidth="1"/>
     <col min="11" max="11" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.3984375" customWidth="1"/>
-    <col min="13" max="15" width="10.8984375" style="21"/>
+    <col min="12" max="12" width="5.375" customWidth="1"/>
+    <col min="13" max="15" width="10.875" style="21"/>
     <col min="16" max="16" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.3984375" customWidth="1"/>
-    <col min="18" max="18" width="7.3984375" style="21" customWidth="1"/>
-    <col min="19" max="19" width="11.09765625" style="21" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="10.8984375" style="21"/>
-    <col min="22" max="22" width="12.09765625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.375" customWidth="1"/>
+    <col min="18" max="18" width="7.375" style="21" customWidth="1"/>
+    <col min="19" max="19" width="11.125" style="21" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="10.875" style="21"/>
+    <col min="22" max="22" width="12.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="J1" s="24" t="s">
         <v>119</v>
       </c>
@@ -1556,22 +1556,22 @@
       </c>
       <c r="P1" s="25">
         <f ca="1">MAX(P6:P12)</f>
-        <v>36381.617479749038</v>
+        <v>36391.708405837468</v>
       </c>
       <c r="V1" s="25">
         <f ca="1">MAX(V6:V12)</f>
-        <v>-35810.623383115744</v>
+        <v>-35821.388086716754</v>
       </c>
       <c r="W1" s="25">
         <f ca="1">P1+V1</f>
-        <v>570.99409663329425</v>
+        <v>570.32031912071398</v>
       </c>
       <c r="X1" s="31">
         <f ca="1">W1/P1</f>
-        <v>1.5694576992106645E-2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:24" s="17" customFormat="1" x14ac:dyDescent="0.3">
+        <v>1.5671710510552203E-2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B2" s="27"/>
       <c r="D2" s="19"/>
       <c r="E2" s="19"/>
@@ -1600,7 +1600,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="3" spans="1:24" s="17" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:24" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="s">
         <v>123</v>
       </c>
@@ -1652,7 +1652,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="4" spans="1:24" s="18" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:24" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="18" t="s">
         <v>132</v>
       </c>
@@ -1708,10 +1708,10 @@
         <v>139</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" s="22">
         <f ca="1">B6-TODAY()</f>
-        <v>-1674</v>
+        <v>-1915</v>
       </c>
       <c r="B6" s="30">
         <v>44372</v>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="K6" s="21">
         <f ca="1">F6/(1+J6*A6/K$1)</f>
-        <v>32074.573383115745</v>
+        <v>32085.338086716754</v>
       </c>
       <c r="M6" s="21">
         <f>D6</f>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="P6" s="25">
         <f ca="1">O6+K6</f>
-        <v>35597.783383115748</v>
+        <v>35608.548086716757</v>
       </c>
       <c r="S6" s="21">
         <f>-E6</f>
@@ -1768,14 +1768,14 @@
       </c>
       <c r="V6" s="25">
         <f ca="1">U6-K6</f>
-        <v>-35810.623383115744</v>
+        <v>-35821.388086716754</v>
       </c>
       <c r="X6" s="25"/>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" s="22">
         <f ca="1">B7-TODAY()</f>
-        <v>-1674</v>
+        <v>-1915</v>
       </c>
       <c r="B7" s="30">
         <v>44372</v>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="K7" s="21">
         <f ca="1">F7/(1+J7*A7/K$1)</f>
-        <v>36083.895056005211</v>
+        <v>36096.005347556347</v>
       </c>
       <c r="M7" s="21">
         <f>D7</f>
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P7" s="25">
         <f ca="1">O7+K7</f>
-        <v>35773.60505600521</v>
+        <v>35785.715347556346</v>
       </c>
       <c r="S7" s="21">
         <f>-E7</f>
@@ -1833,13 +1833,13 @@
       </c>
       <c r="V7" s="25">
         <f ca="1">U7-K7</f>
-        <v>-36263.42505600521</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
+        <v>-36275.535347556346</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" s="22">
         <f ca="1">B8-TODAY()</f>
-        <v>-1674</v>
+        <v>-1915</v>
       </c>
       <c r="B8" s="30">
         <v>44372</v>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="K8" s="21">
         <f ca="1">F8/(1+J8*A8/K$1)</f>
-        <v>40093.21672889468</v>
+        <v>40106.672608395944</v>
       </c>
       <c r="M8" s="21">
         <f>D8</f>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="P8" s="25">
         <f ca="1">O8+K8</f>
-        <v>35764.686728894681</v>
+        <v>35778.142608395945</v>
       </c>
       <c r="S8" s="21">
         <f>-E8</f>
@@ -1897,10 +1897,10 @@
       </c>
       <c r="V8" s="25">
         <f ca="1">U8-K8</f>
-        <v>-36334.596728894678</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
+        <v>-36348.052608395941</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" s="22"/>
       <c r="B9" s="30"/>
       <c r="J9" s="23"/>
@@ -1908,10 +1908,10 @@
       <c r="P9" s="25"/>
       <c r="V9" s="25"/>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" s="22">
         <f ca="1">B10-TODAY()</f>
-        <v>-1639</v>
+        <v>-1880</v>
       </c>
       <c r="B10" s="30">
         <v>44407</v>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="K10" s="21">
         <f ca="1">F10/(1+J10*A10/K$1)</f>
-        <v>30068.44747974904</v>
+        <v>30078.538405837466</v>
       </c>
       <c r="M10" s="21">
         <f>D10</f>
@@ -1952,7 +1952,7 @@
       </c>
       <c r="P10" s="25">
         <f ca="1">O10+K10</f>
-        <v>36381.617479749038</v>
+        <v>36391.708405837468</v>
       </c>
       <c r="S10" s="21">
         <f>-E10</f>
@@ -1968,13 +1968,13 @@
       </c>
       <c r="V10" s="25">
         <f ca="1">U10-K10</f>
-        <v>-37033.397479749037</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
+        <v>-37043.488405837466</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" s="22">
         <f ca="1">B11-TODAY()</f>
-        <v>-1639</v>
+        <v>-1880</v>
       </c>
       <c r="B11" s="30">
         <v>44407</v>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="K11" s="21">
         <f ca="1">F11/(1+J11*A11/K$1)</f>
-        <v>35079.855393040547</v>
+        <v>35091.628140143708</v>
       </c>
       <c r="M11" s="21">
         <f>D11</f>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="P11" s="25">
         <f ca="1">O11+K11</f>
-        <v>36014.005393040548</v>
+        <v>36025.77814014371</v>
       </c>
       <c r="S11" s="21">
         <f>-E11</f>
@@ -2031,13 +2031,13 @@
       </c>
       <c r="V11" s="25">
         <f ca="1">U11-K11</f>
-        <v>-36449.175393040547</v>
-      </c>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
+        <v>-36460.948140143708</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" s="22">
         <f ca="1">B12-TODAY()</f>
-        <v>-1639</v>
+        <v>-1880</v>
       </c>
       <c r="B12" s="30">
         <v>44407</v>
@@ -2062,7 +2062,7 @@
       </c>
       <c r="K12" s="21">
         <f ca="1">F12/(1+J12*A12/K$1)</f>
-        <v>40091.263306332054</v>
+        <v>40104.717874449954</v>
       </c>
       <c r="M12" s="21">
         <f>D12</f>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="P12" s="25">
         <f ca="1">O12+K12</f>
-        <v>35476.913306332055</v>
+        <v>35490.367874449956</v>
       </c>
       <c r="S12" s="21">
         <f>-E12</f>
@@ -2094,10 +2094,10 @@
       </c>
       <c r="V12" s="25">
         <f ca="1">U12-K12</f>
-        <v>-37610.683306332052</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
+        <v>-37624.137874449953</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" s="22"/>
       <c r="B13" s="30"/>
       <c r="J13" s="23"/>
@@ -2105,7 +2105,7 @@
       <c r="P13" s="25"/>
       <c r="V13" s="25"/>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" s="22"/>
       <c r="B14" s="30"/>
       <c r="J14" s="23"/>
@@ -2128,13 +2128,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55101276-AB4B-034D-9CE9-EB07F2069604}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.8984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="43.09765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="53" t="s">
         <v>0</v>
       </c>
@@ -2150,7 +2150,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="55" t="s">
         <v>188</v>
       </c>
@@ -2159,7 +2159,7 @@
       </c>
       <c r="C2" s="1"/>
     </row>
-    <row r="3" spans="1:6" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="55" t="s">
         <v>189</v>
       </c>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="C3" s="1"/>
     </row>
-    <row r="4" spans="1:6" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="55" t="s">
         <v>190</v>
       </c>
@@ -2191,7 +2191,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="55" t="s">
         <v>3</v>
       </c>
@@ -2214,7 +2214,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="55" t="s">
         <v>6</v>
       </c>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="C6" s="1"/>
     </row>
-    <row r="7" spans="1:6" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="55" t="s">
         <v>8</v>
       </c>
@@ -2246,7 +2246,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="55" t="s">
         <v>9</v>
       </c>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="C8" s="1"/>
     </row>
-    <row r="9" spans="1:6" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="55" t="s">
         <v>144</v>
       </c>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="C9" s="1"/>
     </row>
-    <row r="10" spans="1:6" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="55" t="s">
         <v>143</v>
       </c>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C10" s="1"/>
     </row>
-    <row r="11" spans="1:6" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="55" t="s">
         <v>147</v>
       </c>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="C11" s="1"/>
     </row>
-    <row r="12" spans="1:6" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="58" t="s">
         <v>142</v>
       </c>
@@ -2293,15 +2293,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
     </row>
-    <row r="14" spans="1:6" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
     </row>
-    <row r="15" spans="1:6" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="60" t="s">
         <v>11</v>
       </c>
@@ -2309,26 +2309,26 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="61" t="s">
         <v>13</v>
       </c>
       <c r="B16" s="62"/>
       <c r="C16" s="1"/>
     </row>
-    <row r="17" spans="1:3" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="63" t="s">
         <v>14</v>
       </c>
       <c r="B17" s="64"/>
       <c r="C17" s="1"/>
     </row>
-    <row r="18" spans="1:3" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="65"/>
       <c r="B18" s="64"/>
       <c r="C18" s="1"/>
     </row>
-    <row r="19" spans="1:3" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="63" t="str">
         <f>_xlfn.CONCAT("python3 '",B15,".py'")</f>
         <v>python3 'CryptoPriceGrabber.py'</v>
@@ -2336,7 +2336,7 @@
       <c r="B19" s="64"/>
       <c r="C19" s="1"/>
     </row>
-    <row r="20" spans="1:3" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="63" t="str">
         <f>_xlfn.CONCAT("jupyter nbconvert --to script '",B15,".ipynb'")</f>
         <v>jupyter nbconvert --to script 'CryptoPriceGrabber.ipynb'</v>
@@ -2344,7 +2344,7 @@
       <c r="B20" s="64"/>
       <c r="C20" s="1"/>
     </row>
-    <row r="21" spans="1:3" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="66"/>
       <c r="B21" s="67"/>
       <c r="C21" s="1"/>
@@ -2358,23 +2358,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C47E84A-90CC-DA43-AFC7-C13C81E85FE9}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:X27"/>
-  <sheetFormatPr defaultColWidth="10.8984375" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="12.5" style="5" customWidth="1"/>
     <col min="5" max="5" width="26" style="6" customWidth="1"/>
-    <col min="6" max="6" width="9.09765625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.125" style="1" customWidth="1"/>
     <col min="7" max="7" width="12.5" style="5" customWidth="1"/>
-    <col min="8" max="8" width="13.59765625" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.8984375" style="5"/>
+    <col min="8" max="8" width="13.625" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.875" style="5"/>
     <col min="10" max="10" width="10.5" style="5" customWidth="1"/>
-    <col min="11" max="11" width="21.59765625" style="5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.625" style="5" bestFit="1" customWidth="1"/>
     <col min="12" max="13" width="16" style="16" customWidth="1"/>
-    <col min="14" max="17" width="10.8984375" style="5"/>
+    <col min="14" max="17" width="10.875" style="5"/>
     <col min="18" max="20" width="11" customWidth="1"/>
-    <col min="21" max="16384" width="10.8984375" style="1"/>
+    <col min="21" max="16384" width="10.875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>15</v>
       </c>
@@ -2412,7 +2412,7 @@
       <c r="M1" s="15"/>
       <c r="X1" s="3"/>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B2" s="5" t="b">
         <v>1</v>
       </c>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="X2" s="14"/>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="E3" s="4" t="s">
         <v>86</v>
       </c>
@@ -2477,7 +2477,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:24" ht="15" x14ac:dyDescent="0.2">
       <c r="E4" s="4" t="s">
         <v>87</v>
       </c>
@@ -2491,7 +2491,7 @@
       <c r="S4" s="1"/>
       <c r="T4" s="1"/>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:24" ht="15" x14ac:dyDescent="0.2">
       <c r="E5" s="4" t="s">
         <v>88</v>
       </c>
@@ -2514,7 +2514,7 @@
       <c r="S5" s="1"/>
       <c r="T5" s="1"/>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:24" ht="15" x14ac:dyDescent="0.2">
       <c r="E6" s="4" t="s">
         <v>89</v>
       </c>
@@ -2528,7 +2528,7 @@
       <c r="S6" s="1"/>
       <c r="T6" s="1"/>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:24" ht="15" x14ac:dyDescent="0.2">
       <c r="E7" s="4" t="s">
         <v>90</v>
       </c>
@@ -2542,7 +2542,7 @@
       <c r="S7" s="1"/>
       <c r="T7" s="1"/>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:24" ht="15" x14ac:dyDescent="0.2">
       <c r="E8" s="4" t="s">
         <v>91</v>
       </c>
@@ -2565,7 +2565,7 @@
       <c r="S8" s="1"/>
       <c r="T8" s="1"/>
     </row>
-    <row r="9" spans="1:24" s="35" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:24" s="35" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A9" s="32" t="b">
         <v>0</v>
       </c>
@@ -2598,7 +2598,7 @@
       <c r="P9" s="32"/>
       <c r="Q9" s="32"/>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:24" ht="15" x14ac:dyDescent="0.2">
       <c r="E10" s="4" t="s">
         <v>93</v>
       </c>
@@ -2612,7 +2612,7 @@
       <c r="S10" s="1"/>
       <c r="T10" s="1"/>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:24" ht="15" x14ac:dyDescent="0.2">
       <c r="E11" s="4" t="s">
         <v>94</v>
       </c>
@@ -2629,7 +2629,7 @@
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:24" ht="15" x14ac:dyDescent="0.2">
       <c r="B12" s="5" t="b">
         <v>1</v>
       </c>
@@ -2655,7 +2655,7 @@
       <c r="S12" s="1"/>
       <c r="T12" s="1"/>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:24" ht="15" x14ac:dyDescent="0.2">
       <c r="B13" s="5" t="b">
         <v>1</v>
       </c>
@@ -2684,7 +2684,7 @@
       <c r="S13" s="1"/>
       <c r="T13" s="1"/>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:24" ht="15" x14ac:dyDescent="0.2">
       <c r="E14" s="4" t="s">
         <v>98</v>
       </c>
@@ -2698,7 +2698,7 @@
       <c r="S14" s="1"/>
       <c r="T14" s="1"/>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:24" ht="15" x14ac:dyDescent="0.2">
       <c r="E15" s="4" t="s">
         <v>99</v>
       </c>
@@ -2712,7 +2712,7 @@
       <c r="S15" s="1"/>
       <c r="T15" s="1"/>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:24" ht="15" x14ac:dyDescent="0.2">
       <c r="E16" s="4" t="s">
         <v>100</v>
       </c>
@@ -2738,7 +2738,7 @@
       <c r="S16" s="1"/>
       <c r="T16" s="1"/>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:20" ht="15" x14ac:dyDescent="0.2">
       <c r="B17" s="5" t="s">
         <v>101</v>
       </c>
@@ -2761,7 +2761,7 @@
       <c r="S17" s="1"/>
       <c r="T17" s="1"/>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:20" ht="15" x14ac:dyDescent="0.2">
       <c r="E18" s="4" t="s">
         <v>103</v>
       </c>
@@ -2772,7 +2772,7 @@
       <c r="S18" s="1"/>
       <c r="T18" s="1"/>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:20" ht="15" x14ac:dyDescent="0.2">
       <c r="E19" s="4" t="s">
         <v>104</v>
       </c>
@@ -2792,7 +2792,7 @@
       <c r="S19" s="1"/>
       <c r="T19" s="1"/>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:20" ht="15" x14ac:dyDescent="0.2">
       <c r="E20" s="4" t="s">
         <v>106</v>
       </c>
@@ -2821,7 +2821,7 @@
       <c r="S20" s="1"/>
       <c r="T20" s="1"/>
     </row>
-    <row r="21" spans="1:20" s="35" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:20" s="35" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A21" s="32" t="b">
         <v>0</v>
       </c>
@@ -2860,7 +2860,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="E22" s="49" t="s">
         <v>110</v>
       </c>
@@ -2869,7 +2869,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="C23" s="1" t="s">
         <v>112</v>
       </c>
@@ -2877,17 +2877,17 @@
         <v>113</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B24" s="1" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="K25" s="5" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="C26" s="5" t="s">
         <v>116</v>
       </c>
@@ -2898,7 +2898,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="C27" s="5" t="s">
         <v>118</v>
       </c>
@@ -2924,25 +2924,25 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFB2DD8E-60DC-3B4A-A267-EE8D8D5A0035}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:Q31"/>
-  <sheetFormatPr defaultColWidth="10.8984375" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="13.59765625" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="13.625" style="5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14" style="5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.5" style="5" customWidth="1"/>
-    <col min="5" max="5" width="14.3984375" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.09765625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="9.8984375" style="41" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.375" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9.875" style="41" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="25.59765625" style="5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="37.09765625" style="16" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="25.625" style="5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="37.125" style="16" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="30.5" style="17" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16" style="17" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11" style="17"/>
-    <col min="14" max="14" width="25.59765625" style="5" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="10.8984375" style="1"/>
+    <col min="14" max="14" width="25.625" style="5" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="10.875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>15</v>
       </c>
@@ -2987,7 +2987,7 @@
       </c>
       <c r="Q1" s="3"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="E2" s="49" t="s">
         <v>29</v>
       </c>
@@ -2996,7 +2996,7 @@
       <c r="J2" s="46"/>
       <c r="Q2" s="14"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="E3" s="49" t="s">
         <v>30</v>
       </c>
@@ -3015,7 +3015,7 @@
       </c>
       <c r="Q3" s="14"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="E4" s="49" t="s">
         <v>34</v>
       </c>
@@ -3024,7 +3024,7 @@
       <c r="J4" s="46"/>
       <c r="Q4" s="14"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>35</v>
       </c>
@@ -3057,7 +3057,7 @@
       <c r="L5" s="5"/>
       <c r="M5" s="5"/>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>35</v>
       </c>
@@ -3099,7 +3099,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>35</v>
       </c>
@@ -3141,7 +3141,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>35</v>
       </c>
@@ -3179,7 +3179,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>53</v>
       </c>
@@ -3223,7 +3223,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="b">
         <v>1</v>
       </c>
@@ -3256,7 +3256,7 @@
       <c r="L10" s="5"/>
       <c r="M10" s="5"/>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>63</v>
       </c>
@@ -3289,10 +3289,10 @@
       <c r="L11" s="5"/>
       <c r="M11" s="5"/>
     </row>
-    <row r="12" spans="1:17" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:17" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F12"/>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C13" s="1"/>
       <c r="F13"/>
       <c r="I13" s="37" t="s">
@@ -3302,7 +3302,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:17" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C14" s="1"/>
       <c r="F14"/>
       <c r="I14" s="39" t="s">
@@ -3312,75 +3312,75 @@
         <v>72</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="E15" s="5"/>
       <c r="F15"/>
       <c r="G15" s="5"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="E16" s="1"/>
       <c r="F16"/>
       <c r="G16" s="5"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
     </row>
-    <row r="17" spans="6:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F17"/>
       <c r="I17" s="1"/>
     </row>
-    <row r="18" spans="6:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F18"/>
       <c r="I18" s="1"/>
     </row>
-    <row r="19" spans="6:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F19"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="20" spans="6:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F20"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
     </row>
-    <row r="21" spans="6:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F21"/>
       <c r="I21" s="1"/>
     </row>
-    <row r="22" spans="6:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F22"/>
       <c r="I22" s="1"/>
     </row>
-    <row r="23" spans="6:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F23"/>
       <c r="I23" s="1"/>
     </row>
-    <row r="24" spans="6:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F24"/>
       <c r="I24" s="1"/>
     </row>
-    <row r="25" spans="6:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F25"/>
     </row>
-    <row r="26" spans="6:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F26"/>
     </row>
-    <row r="27" spans="6:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F27"/>
     </row>
-    <row r="28" spans="6:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F28"/>
     </row>
-    <row r="29" spans="6:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F29"/>
     </row>
-    <row r="30" spans="6:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F30"/>
     </row>
-    <row r="31" spans="6:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F31" s="32"/>
     </row>
   </sheetData>
@@ -3408,22 +3408,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{967B387A-0290-FE4F-937F-0434C3D9690D}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:K27"/>
-  <sheetFormatPr defaultColWidth="10.8984375" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.3984375" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="17.59765625" style="43" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.3984375" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.09765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.59765625" style="44" customWidth="1"/>
-    <col min="8" max="8" width="16.8984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.8984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.375" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="17.625" style="43" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.375" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.625" style="44" customWidth="1"/>
+    <col min="8" max="8" width="16.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.875" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.8984375" style="44" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="10.8984375" style="1"/>
+    <col min="11" max="11" width="14.875" style="44" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="10.875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B1" s="9" t="s">
         <v>152</v>
       </c>
@@ -3437,7 +3437,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B2" s="81">
         <f>C2-C6</f>
         <v>-4995.8000000000029</v>
@@ -3453,18 +3453,18 @@
         <v>-4997</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B3" s="82"/>
       <c r="C3" s="87"/>
       <c r="D3" s="87"/>
       <c r="E3" s="82"/>
     </row>
-    <row r="4" spans="1:9" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="75">
         <v>44473.661527777775</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="83">
         <f>AVERAGE(C6:D6)</f>
         <v>49211.4</v>
@@ -3484,7 +3484,7 @@
       </c>
       <c r="I5" s="10"/>
     </row>
-    <row r="6" spans="1:9" ht="15.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="85"/>
       <c r="B6" s="86"/>
       <c r="C6" s="50">
@@ -3504,11 +3504,11 @@
         <v>-8.8000000000029104</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
     </row>
-    <row r="8" spans="1:9" ht="18" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:9" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
         <v>19</v>
       </c>
@@ -3528,7 +3528,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>36</v>
       </c>
@@ -3544,7 +3544,7 @@
         <v>4.3899999999994179</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>39</v>
       </c>
@@ -3564,7 +3564,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>43</v>
       </c>
@@ -3584,7 +3584,7 @@
         <v>8.2399999999979627</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>48</v>
       </c>
@@ -3604,72 +3604,72 @@
         <v>9.9999999998544808E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="18" x14ac:dyDescent="0.25">
       <c r="B13" s="11"/>
       <c r="E13" s="11"/>
       <c r="F13" s="74"/>
       <c r="I13" s="13"/>
     </row>
-    <row r="14" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="18" x14ac:dyDescent="0.25">
       <c r="B14" s="11"/>
       <c r="E14" s="11"/>
       <c r="F14" s="12"/>
       <c r="I14" s="13"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B15" s="11"/>
       <c r="E15" s="11"/>
       <c r="F15" s="12"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B16" s="11"/>
       <c r="E16" s="11"/>
       <c r="F16" s="12"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B17" s="11"/>
       <c r="E17" s="11"/>
       <c r="F17" s="12"/>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B18" s="11"/>
       <c r="E18" s="11"/>
       <c r="F18" s="12"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B19" s="11"/>
       <c r="E19" s="11"/>
       <c r="F19" s="12"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B20" s="11"/>
       <c r="E20" s="11"/>
       <c r="F20" s="12"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B21" s="11"/>
       <c r="E21" s="11"/>
       <c r="F21" s="12"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="11"/>
       <c r="E22" s="11"/>
       <c r="F22" s="12"/>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B23" s="11"/>
       <c r="F23" s="12"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B24" s="11"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B25" s="11"/>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B26" s="11"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B27" s="11"/>
     </row>
   </sheetData>
@@ -3708,17 +3708,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00C53218-450D-FB48-842A-44BA3A717B4E}">
   <dimension ref="A1:F20"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.8984375" customWidth="1"/>
-    <col min="3" max="3" width="54.8984375" style="17" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.875" customWidth="1"/>
+    <col min="3" max="3" width="54.875" style="17" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="73.5" style="17" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="33.59765625" style="17" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="58.09765625" style="17" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.625" style="17" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="58.125" style="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="78" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" s="78" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>191</v>
       </c>
@@ -3738,7 +3738,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="b">
         <v>1</v>
       </c>
@@ -3758,7 +3758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="b">
         <v>1</v>
       </c>
@@ -3778,7 +3778,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="b">
         <v>1</v>
       </c>
@@ -3798,12 +3798,12 @@
         <v>158</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="b">
         <v>1</v>
       </c>
@@ -3820,7 +3820,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="b">
         <v>1</v>
       </c>
@@ -3837,7 +3837,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="b">
         <v>1</v>
       </c>
@@ -3857,7 +3857,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="b">
         <v>1</v>
       </c>
@@ -3874,7 +3874,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="b">
         <v>1</v>
       </c>
@@ -3894,12 +3894,12 @@
         <v>185</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="b">
         <v>1</v>
       </c>
@@ -3913,7 +3913,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="b">
         <v>1</v>
       </c>
@@ -3927,7 +3927,7 @@
         <v>3.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="b">
         <v>1</v>
       </c>
@@ -3944,7 +3944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="b">
         <v>1</v>
       </c>
@@ -3955,7 +3955,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="b">
         <v>1</v>
       </c>
@@ -3972,12 +3972,12 @@
         <v>1.4999999999999999E-4</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="b">
         <v>1</v>
       </c>
@@ -3997,7 +3997,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="b">
         <v>1</v>
       </c>
@@ -4017,7 +4017,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="b">
         <v>1</v>
       </c>
